--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_102_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_102_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2475</v>
+        <v>4.4931</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0691</v>
+        <v>5.4491</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8216</v>
+        <v>-0.956</v>
       </c>
       <c r="G2" t="n">
         <v>2.6043</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9653</v>
+        <v>1.2109</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3343</v>
+        <v>1.7144</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.369</v>
+        <v>-0.5034</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.414</v>
+        <v>2.3747</v>
       </c>
       <c r="E3" t="n">
-        <v>2.158</v>
+        <v>2.1008</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2561</v>
+        <v>0.274</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1674</v>
+        <v>1.4408</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2641</v>
+        <v>-0.6773</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9033</v>
+        <v>2.1181</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9349</v>
+        <v>1.2626</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3802</v>
+        <v>0.1351</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3151</v>
+        <v>1.1275</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2325</v>
+        <v>0.1782</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6443</v>
+        <v>-0.8123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4118</v>
+        <v>0.9906</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2025</v>
+        <v>1.1479</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8916</v>
+        <v>0.6216</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3109</v>
+        <v>0.5263</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5387</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7527</v>
+        <v>1.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.214</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2019</v>
+        <v>2.1732</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6591</v>
+        <v>1.3204</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.8528</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4408</v>
+        <v>-1.1674</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6773</v>
+        <v>-0.2641</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1181</v>
+        <v>-0.9033</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2626</v>
+        <v>-0.9349</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1351</v>
+        <v>0.3802</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1275</v>
+        <v>-1.3151</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1782</v>
+        <v>-0.2325</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8123</v>
+        <v>-0.6443</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9906</v>
+        <v>0.4118</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9751</v>
+        <v>1.9617</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1799</v>
+        <v>1.0541</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7951</v>
+        <v>0.9076</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6778999999999999</v>
+        <v>2.5387</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>3.7527</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2862</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.8466</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6836</v>
+        <v>1.2615</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6166</v>
+        <v>-0.4149</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0673</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5614</v>
+        <v>0.2181</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1142</v>
+        <v>0.6921</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6756</v>
+        <v>-0.474</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5599</v>
+        <v>0.2763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6737</v>
+        <v>-0.6129</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2336</v>
+        <v>0.8892</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2262</v>
+        <v>0.131</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4237</v>
+        <v>-1.1237</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1975</v>
+        <v>1.2548</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2683</v>
+        <v>0.2313</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1211</v>
+        <v>-0.7121</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>0.9435</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4945</v>
+        <v>-0.1003</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5448</v>
+        <v>-0.4116</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0502</v>
+        <v>0.3113</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4033</v>
+        <v>0.1838</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2636</v>
+        <v>-0.1098</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6669</v>
+        <v>0.2937</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1418</v>
+        <v>0.4254</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1418</v>
+        <v>0.4254</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6398</v>
+        <v>-0.1507</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1594</v>
+        <v>1.0157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5196</v>
+        <v>-1.1664</v>
       </c>
       <c r="G7" t="n">
-        <v>0.131</v>
+        <v>-1.2262</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1237</v>
+        <v>-1.4237</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2548</v>
+        <v>0.1975</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2313</v>
+        <v>0.2683</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7121</v>
+        <v>0.1211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9435</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1003</v>
+        <v>-1.4945</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4116</v>
+        <v>-1.5448</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3113</v>
+        <v>0.0502</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7323</v>
+        <v>0.0059</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6563</v>
+        <v>0.6056</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.076</v>
+        <v>-0.5996</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4254</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4254</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8874</v>
+        <v>-1.1641</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2068</v>
+        <v>-2.1139</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3194</v>
+        <v>0.9498</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2893</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6339</v>
+        <v>1.3572</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8804</v>
+        <v>0.2126</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5143</v>
+        <v>1.1446</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6143</v>
+        <v>-1.8325</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3774</v>
+        <v>-3.8309</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7631</v>
+        <v>1.9984</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1425</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0075</v>
+        <v>0.7892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>-0.1845</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7385</v>
+        <v>0.9737</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6414</v>
+        <v>-1.9354</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2565</v>
+        <v>0.147</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3849</v>
+        <v>-2.0824</v>
       </c>
       <c r="G10" t="n">
         <v>0.3037</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0353</v>
+        <v>-0.3293</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8962</v>
+        <v>0.5074</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1391</v>
+        <v>-0.8366</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.587700000000001</v>
+        <v>5.081199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.243400000000002</v>
+        <v>4.736799999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3442999999999996</v>
+        <v>0.3445</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4129000000000001</v>
+        <v>-0.4129000000000005</v>
       </c>
       <c r="H11" t="n">
         <v>-9.597899999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>9.185</v>
+        <v>9.184999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>5.3261</v>
@@ -1291,13 +1291,13 @@
         <v>-2.0672</v>
       </c>
       <c r="L11" t="n">
-        <v>7.3936</v>
+        <v>7.393600000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-5.7392</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.5306</v>
+        <v>-7.530600000000001</v>
       </c>
       <c r="O11" t="n">
         <v>1.7914</v>
@@ -1312,16 +1312,16 @@
         <v>10.438</v>
       </c>
       <c r="S11" t="n">
-        <v>5.052</v>
+        <v>6.545400000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6197</v>
+        <v>5.1135</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4322</v>
+        <v>1.4323</v>
       </c>
       <c r="V11" t="n">
-        <v>2.427999999999999</v>
+        <v>2.428</v>
       </c>
       <c r="W11" t="n">
         <v>8.214399999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5745</v>
+        <v>4.1706</v>
       </c>
       <c r="E12" t="n">
-        <v>0.833</v>
+        <v>1.5408</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7414</v>
+        <v>2.6299</v>
       </c>
       <c r="G12" t="n">
         <v>3.3373</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8503</v>
+        <v>-1.2542</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4857</v>
+        <v>-0.778</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3646</v>
+        <v>-0.4762</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5522</v>
+        <v>4.0069</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6791</v>
+        <v>2.0329</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8732</v>
+        <v>1.974</v>
       </c>
       <c r="G13" t="n">
         <v>2.9309</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0925</v>
+        <v>-0.6379</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0376</v>
+        <v>-0.6838</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0549</v>
+        <v>0.0459</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7765</v>
+        <v>2.7157</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0192</v>
+        <v>2.1372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7573</v>
+        <v>0.5785</v>
       </c>
       <c r="G14" t="n">
         <v>2.352</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.639</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4007</v>
+        <v>-0.2827</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1775</v>
+        <v>-0.3563</v>
       </c>
       <c r="V14" t="n">
         <v>1.4665</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9805</v>
+        <v>1.5474</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1506</v>
+        <v>2.2686</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1701</v>
+        <v>-0.7211</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1684</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4594</v>
+        <v>-0.8924</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8619</v>
+        <v>-0.4129</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2812</v>
+        <v>-0.4349</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0041</v>
+        <v>0.7684</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2853</v>
+        <v>-1.2033</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0937</v>
+        <v>0.3807</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9101</v>
+        <v>-0.6231</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8164</v>
+        <v>1.0038</v>
       </c>
       <c r="J16" t="n">
-        <v>1.562</v>
+        <v>0.9492</v>
       </c>
       <c r="K16" t="n">
-        <v>1.378</v>
+        <v>-0.2654</v>
       </c>
       <c r="L16" t="n">
-        <v>0.184</v>
+        <v>1.2146</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4683</v>
+        <v>-0.5684</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5321</v>
+        <v>-0.3577</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0004</v>
+        <v>-0.2108</v>
       </c>
       <c r="P16" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1432</v>
+        <v>-0.2074</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6018</v>
+        <v>-0.1808</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4586</v>
+        <v>-0.0266</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7501</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3356</v>
+        <v>-0.8113</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5727</v>
+        <v>-1.4217</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9083</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2674</v>
+        <v>0.0152</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8127</v>
+        <v>-0.1788</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5453</v>
+        <v>0.1941</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9142</v>
+        <v>0.0368</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8773</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6468</v>
+        <v>-0.0216</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.1788</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5821</v>
+        <v>0.1573</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6469</v>
+        <v>-0.1307</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8363</v>
+        <v>-0.2987</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1893</v>
+        <v>0.168</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5865</v>
+        <v>-1.0318</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6504</v>
+        <v>0.5238</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2369</v>
+        <v>-1.5556</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3807</v>
+        <v>0.7382</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6231</v>
+        <v>2.1368</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0038</v>
+        <v>-1.3986</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9492</v>
+        <v>1.1526</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2654</v>
+        <v>1.8654</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2146</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5684</v>
+        <v>-0.4144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3577</v>
+        <v>0.2714</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2108</v>
+        <v>-0.6859</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3589</v>
+        <v>-0.002</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2987</v>
+        <v>0.5309</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0602</v>
+        <v>-0.5329</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9121</v>
+        <v>-1.0397</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4217</v>
+        <v>0.1785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5096000000000001</v>
+        <v>-1.2181</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0152</v>
+        <v>1.0937</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1788</v>
+        <v>1.9101</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1941</v>
+        <v>-0.8164</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0368</v>
+        <v>1.562</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.378</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.184</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0216</v>
+        <v>-0.4683</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1788</v>
+        <v>0.5321</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>-1.0004</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2315</v>
+        <v>-0.6152</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.2238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0672</v>
+        <v>-0.3914</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0826</v>
+        <v>-1.1835</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4058</v>
+        <v>-0.4889</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4884</v>
+        <v>-0.6946</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7382</v>
+        <v>0.2674</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1368</v>
+        <v>0.8127</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3986</v>
+        <v>-0.5453</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1526</v>
+        <v>0.9142</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8654</v>
+        <v>0.8773</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4144</v>
+        <v>-0.6468</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2714</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>-0.5821</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0527</v>
+        <v>0.7991</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4129</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4657</v>
+        <v>0.0244</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1959</v>
+        <v>-2.0558</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7042</v>
+        <v>-0.8222</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4917</v>
+        <v>-1.2336</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4283</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2324</v>
+        <v>0.3725</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3462</v>
+        <v>0.2282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1138</v>
+        <v>0.1443</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4383</v>
+        <v>-3.456</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7995</v>
+        <v>-4.2098</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3613</v>
+        <v>0.7538</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0773</v>
@@ -2170,13 +2170,13 @@
         <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1444</v>
+        <v>-0.1621</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6247</v>
+        <v>-0.0349</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1272</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6393</v>
+        <v>-4.4427</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7339</v>
+        <v>-2.8519</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9054</v>
+        <v>-1.5909</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0285</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3066</v>
+        <v>-0.11</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1142</v>
+        <v>-0.0037</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4208</v>
+        <v>-0.1063</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.587800000000001</v>
+        <v>-2.015100000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3443999999999994</v>
+        <v>-0.3443000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.2433</v>
+        <v>-1.670599999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4128999999999987</v>
+        <v>0.4129000000000005</v>
       </c>
       <c r="H24" t="n">
         <v>9.597899999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.185</v>
+        <v>-9.184999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>5.739499999999998</v>
@@ -2311,7 +2311,7 @@
         <v>-5.3263</v>
       </c>
       <c r="N24" t="n">
-        <v>2.067400000000001</v>
+        <v>2.0674</v>
       </c>
       <c r="O24" t="n">
         <v>-7.3936</v>
@@ -2326,13 +2326,13 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.0519</v>
+        <v>-3.4793</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.432199999999999</v>
+        <v>-1.4321</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.6198</v>
+        <v>-2.0472</v>
       </c>
       <c r="V24" t="n">
         <v>-2.428</v>
